--- a/신고신저가_20260904.xlsx
+++ b/신고신저가_20260904.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -76,15 +77,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,84 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 2026년 9월 3일 시장은 미국의 성장주·가상자산 반등과 아시아의 금융·상사주 강세가 핵심이었다. 다만 미국 전자기술과 홍콩 전기차에는 신저가가 남아 지수 상승보다 내부 차별화가 컸다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(9/3): S&amp;P500과 나스닥이 각각 1.06%, 1.40% 올랐고 신고가 71종이 신저가 42종을 웃돌았다. 기술서비스는 순신고가가 14종, 헬스케어는 12종이었다. 비트코인이 8만1000달러대로 오르며 스트래티지·로빈후드·서클이 16% 이상 뛰었고, 스노우플레이크는 제품매출 37% 증가와 연간 전망 상향으로 16.55% 올랐다. 반면 전자기술은 신저가가 신고가보다 13종 많았으며 브로드컴과 시에나는 호실적에도 높아진 기대를 충족하지 못했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(9/3): 닛케이225는 외부 마감자료 기준 0.17% 내렸지만 TOPIX는 0.50% 올랐다. 금융은 순신고가 4종, 유통서비스는 3종이었다. 버크셔해서웨이의 추가매수 가능성 발언으로 미쓰비시상사·스미토모상사·미쓰이물산이 2.62~4.09% 상승했다. 니토리는 8월 기존점 매출 증가로 8.41% 급등한 반면 엔화 강세와 금리인상 관측은 부동산에 부담이었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(9/3): 항셍지수는 0.39%, 항셍테크는 1.08% 내렸지만 금융에서는 신고가 11종이 나와 방어적 매수가 뚜렷했다. 앤커이노베이션은 2분기 이익 호조로 2.37% 올랐고 중광핵전력은 원전 성장 기대가 이어졌다. 반면 샤오펑은 상반기 손실 확대와 가격경쟁 우려로 신저가를 기록했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(9/3): 상해종합과 CSI300은 각각 0.02%, 0.10% 올라 보합권이었지만 상승 종목 수는 전체의 약 3분의 1에 그쳤다. 금융은 순신고가 14종으로 압도적이었고 보험 업종은 2.58% 상승했다. 중국태평양보험이 3.69% 올랐고 산둥골드는 귀금속 강세로 장중 고점을 높였다. 반면 반도체 상장지수펀드는 0.6% 하락해 옴니비전 신저가와 방향이 같았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ① 비트코인 8만달러선 유지와 가상자산 관련주의 거래대금이 함께 지속되는지 본다. ② 스노우플레이크의 제품매출 가속이 다음 분기 소비 기반 매출로 이어지는지 확인한다. ③ 일본 상사주 추가매수 기대와 엔화 강세 중 어느 힘이 더 오래가는지 비교한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 배울점: 좋은 실적과 좋은 주가는 같은 말이 아니다. 브로드컴과 시에나는 매출과 이익이 예상을 웃돌았지만 주가가 내렸다. 시장이 이미 더 높은 성장률과 가이던스를 가격에 넣었다면 실제 숫자가 좋아도 기대치보다 낮은 순간 밸류에이션이 줄어든다. 다음 실적에서는 단순 전년 대비 성장보다 회사 전망과 시장 예상의 차이를 먼저 봐야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 모든 top_movers의 실제 거래 기준일은 2026년 9월 3일 현지장 마감이며, 미국장은 KST 2026년 9월 4일 새벽 마감분이다. 일본 index CSV는 2026년 9월 2일 값으로 하루 지연되어 닛케이 수치는 2026년 9월 3일 외부 마감자료로 보완했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +791,19 @@
       <c r="C2" t="n">
         <v>7747.71</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.22</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>0.31</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>2.15</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="4" t="n">
         <v>13.18</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +829,19 @@
       <c r="C3" t="n">
         <v>26584.06</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.16</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <v>-0.92</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>14.38</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +867,19 @@
       <c r="C4" t="n">
         <v>6562.72</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>-3.99</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>-3.61</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>4.88</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="5" t="n">
         <v>-25.44</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>55.73</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +905,19 @@
       <c r="C5" t="n">
         <v>64325.64</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>-2.85</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>-2.92</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <v>-5.96</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>27.78</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +943,19 @@
       <c r="C6" t="n">
         <v>3942.09</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.02</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>-0.37</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="4" t="n">
         <v>1.64</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="5" t="n">
         <v>-2.13</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>-0.67</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +981,19 @@
       <c r="C7" t="n">
         <v>4552.58</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>-1.68</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="5" t="n">
         <v>-2.27</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="5" t="n">
         <v>-5.49</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>-1.67</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +1019,19 @@
       <c r="C8" t="n">
         <v>25213.31</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="5" t="n">
         <v>-0.39</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>-1.38</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="5" t="n">
         <v>-2.71</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="5" t="n">
         <v>-0.16</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="5" t="n">
         <v>-1.63</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1057,19 @@
       <c r="C9" t="n">
         <v>4468.48</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="5" t="n">
         <v>-1.08</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>-3.29</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="5" t="n">
         <v>-9.42</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="5" t="n">
         <v>-10.19</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="5" t="n">
         <v>-18.99</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1188,7 @@
       <c r="F2" t="n">
         <v>14</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1229,7 @@
       <c r="F3" t="n">
         <v>12</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1270,7 @@
       <c r="F4" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1311,7 @@
       <c r="F5" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1352,7 @@
       <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1393,7 @@
       <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1434,7 @@
       <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1475,7 @@
       <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1516,7 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1557,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1598,7 @@
       <c r="F12" t="n">
         <v>-1</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1557,7 +1639,7 @@
       <c r="F13" t="n">
         <v>-1</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1598,7 +1680,7 @@
       <c r="F14" t="n">
         <v>-1</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1639,7 +1721,7 @@
       <c r="F15" t="n">
         <v>-4</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1680,7 +1762,7 @@
       <c r="F16" t="n">
         <v>-5</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1721,7 +1803,7 @@
       <c r="F17" t="n">
         <v>-13</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +2006,7 @@
       <c r="F22" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1965,7 +2047,7 @@
       <c r="F23" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2004,7 +2086,7 @@
       <c r="F24" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2043,7 +2125,7 @@
       <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2084,7 +2166,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2123,7 +2205,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2162,7 +2244,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2201,7 +2283,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2240,7 +2322,7 @@
       <c r="F30" t="n">
         <v>-1</v>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2281,7 +2363,7 @@
       <c r="F31" t="n">
         <v>-1</v>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2320,7 +2402,7 @@
       <c r="F32" t="n">
         <v>-2</v>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2677,7 +2759,7 @@
       <c r="F41" t="n">
         <v>11</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2718,7 +2800,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2759,7 +2841,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2798,7 +2880,7 @@
       <c r="F44" t="n">
         <v>-1</v>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2837,7 +2919,7 @@
       <c r="F45" t="n">
         <v>-1</v>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2876,7 +2958,7 @@
       <c r="F46" t="n">
         <v>-2</v>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3393,7 +3475,7 @@
       <c r="F59" t="n">
         <v>14</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3434,7 +3516,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3473,7 +3555,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3514,7 +3596,7 @@
       <c r="F62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3553,7 +3635,7 @@
       <c r="F63" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3592,7 +3674,7 @@
       <c r="F64" t="n">
         <v>-1</v>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3631,7 +3713,7 @@
       <c r="F65" t="n">
         <v>-1</v>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3672,7 +3754,7 @@
       <c r="F66" t="n">
         <v>-1</v>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4103,30 +4185,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4147,90 +4230,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4252,58 +4340,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>당일 1.3% 반등했지만 3개월 -3.6%이고 전자기술 신저가 우위라 종목별 차별화가 크다.</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4323,58 +4416,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.2%, 3개월 14.4% 상승했고 헬스케어 신고가 우위가 중기 강세를 확인했다.</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>14.4</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>12.9</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4394,58 +4492,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>당일 1.6%, 3개월 12.6% 올라 금융주의 상대강도와 신고가 확산이 함께 나타났다.</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4465,58 +4568,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>당일 1.4% 반등했지만 1개월 -1.8%로 소비 경기 회복 신호는 아직 약하다.</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4536,58 +4644,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.9%, 1주 1.8% 올라 대형 플랫폼주 중심의 단기 회복이 이어졌다.</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4607,58 +4720,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>당일 1.0% 올랐지만 1개월 -6.3%여서 산업재의 중기 추세 회복은 더 확인해야 한다.</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>-6.3</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4678,58 +4796,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.3%로 밀렸지만 3개월 4.6% 상승해 방어적 흐름은 유지됐다.</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>11.1</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4749,58 +4872,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.7%였지만 1개월 12.8%, 연초 이후 46.5%로 원유 강세의 수혜가 누적됐다.</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>46.5</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4820,58 +4948,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.8% 반등했지만 1개월 -1.4%라 금리 부담이 완전히 해소되지는 않았다.</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4891,58 +5024,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.6%로 약했지만 3개월 2.3% 상승해 중기 흐름은 보합권을 지켰다.</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4962,58 +5100,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>당일 1.2% 반등했지만 1개월 -2.1%로 금리 민감 업종의 부담이 남았다.</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>11.4</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>6</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5033,58 +5176,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>11.7</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5104,58 +5248,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5175,58 +5320,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>14</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5246,58 +5392,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>8</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5317,58 +5464,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>11.9</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>12</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5388,58 +5536,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5459,58 +5608,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>-5.4</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>43.1</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5530,58 +5680,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>14.1</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>10</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5601,58 +5752,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>-7.6</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>4</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5672,58 +5824,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>11</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5743,58 +5896,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>15.4</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>15.3</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>9</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5814,58 +5968,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>13</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5885,58 +6040,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>6</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5956,58 +6112,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>15</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6027,58 +6184,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>54</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6098,58 +6256,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6169,58 +6328,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6240,58 +6400,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6311,58 +6472,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-5.4</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6382,56 +6544,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>-9.5</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-10</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-18.7</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6449,58 +6612,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.6%, 1주 -5.6%로 밀렸지만 연초 이후 37.2% 상승해 차익실현 성격이 강하다.</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6520,58 +6688,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.8%, 3개월 -10.6%로 중국 기술주의 중기 조정이 이어졌다.</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>-4.9</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6591,58 +6764,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.5%, 3개월 -18.6%로 통신 성장주의 하락 추세가 여전히 무겁다.</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>32.3</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6662,56 +6840,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>당일 1.1% 반등했지만 3개월 -15.7%라 전기차 가격경쟁 부담이 남아 있다.</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>-5.4</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-15.8</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>8</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6729,58 +6912,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.2%였지만 1주 1.7% 상승해 지정학적 긴장 속 방산주의 방어력이 유지됐다.</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-10.5</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-17</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>11</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6800,56 +6988,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.1%, 3개월 -22.1%로 공급과잉과 수익성 우려가 태양광 약세에 남아 있다.</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>-5.3</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-22.1</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-15.8</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6867,58 +7060,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.5%, 연초 이후 -21.5%로 주류 소비의 구조적 약세가 지속됐다.</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-21.5</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>13</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6938,58 +7136,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.5%였지만 3개월 7.1% 상승했고 개별 은행 신고가 확산이 방어력을 보였다.</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>7.1</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>4</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7009,58 +7212,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>당일 1.4%로 강했지만 1주 -2.7%여서 유색금속의 추세 반전은 더 확인해야 한다.</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>6</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7080,58 +7288,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.7% 반등했지만 연초 이후 -18.9%로 부동산의 구조적 신뢰 약세가 이어졌다.</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-6.2</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-18.9</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>12</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7151,58 +7364,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.7% 반등했지만 1개월 -1.0%로 거래대금 둔화 부담이 남았다.</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7222,58 +7440,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.5%, 3개월 15.9% 상승해 방어적 성장 성격이 유지됐다.</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>5</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7293,58 +7516,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.4%, 연초 이후 -16.1%로 소비 회복 기대가 가격에 연결되지 못했다.</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-16.1</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7356,7 +7584,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1.3"/>
@@ -7368,7 +7596,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-5.6"/>
@@ -7380,7 +7608,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-9.5"/>
@@ -7392,7 +7620,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-22.1"/>
@@ -7404,7 +7632,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-21.5"/>
@@ -7416,7 +7644,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7428,7 +7656,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7440,7 +7668,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7452,7 +7680,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7464,7 +7692,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7476,7 +7704,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7590,12 +7818,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7637,10 +7865,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>브로드컴(반도체·인프라 소프트웨어): 실적은 예상을 웃돌았지만 4분기 매출 전망이 높아진 시장 기대에 못 미쳤다.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7689,10 +7921,10 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7741,10 +7973,10 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7793,15 +8025,15 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7847,15 +8079,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7899,15 +8131,15 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7951,10 +8183,10 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8003,10 +8235,10 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8055,10 +8287,10 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8111,19 +8343,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 디어(농기계): 베어드가 투자의견을 상향하고 목표가를 800달러로 높임</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8169,15 +8401,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8221,10 +8453,10 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8277,14 +8509,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>(전일) 화이자(글로벌 제약): 2분기 실적 호조 이후 방어주 선호가 이어짐</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8337,14 +8569,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>(전일) 코노코필립스(원유·가스 생산): 미·이란 충돌에 따른 유가 급등</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8397,14 +8629,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr">
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>(전일) TJX(티제이맥스·마셜스 할인 유통): 마막스 부문 둔화를 짚은 투자의견 하향 여파</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8457,15 +8689,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8509,15 +8741,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>스노우플레이크(클라우드 데이터 플랫폼): 2분기 제품매출이 37% 늘고 연간 제품매출 전망을 60억7000만달러로 상향했다.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8561,15 +8797,15 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8617,10 +8853,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8669,15 +8905,15 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8721,10 +8957,14 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>로빈후드(온라인 증권사): 비트코인 급등과 가상자산 거래 활성화 기대가 거래수익 전망을 끌어올렸다.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8777,10 +9017,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8827,10 +9067,10 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8883,14 +9123,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr">
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>(전일) 발레로(정유): 특별한 뉴스 없음. 정유마진과 에너지 업종 강세에 따른 흐름으로 추정한다.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8943,14 +9183,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr">
+      <c r="N26" s="10" t="inlineStr">
         <is>
           <t>(전일) 캐나디안내추럴(오일샌드 생산): 미·이란 충돌로 국제유가 급등</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9003,10 +9243,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9055,19 +9295,19 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="8" t="inlineStr">
+      <c r="N28" s="10" t="inlineStr">
         <is>
           <t>(전일) 컨스텔레이션에너지(원전 발전사): 원전 장기계약과 상향 가이던스 기대가 지속</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9111,15 +9351,15 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9163,10 +9403,10 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="8" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9213,10 +9453,10 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" s="8" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9269,14 +9509,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N32" s="8" t="inlineStr">
+      <c r="N32" s="10" t="inlineStr">
         <is>
           <t>(전일) 리제네론(바이오의약품): 호실적 이후 제약·바이오 강세가 이어지며 신고가</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9325,10 +9565,10 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" s="8" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9377,15 +9617,15 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="8" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9433,15 +9673,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9485,15 +9725,15 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="8" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9535,10 +9775,10 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="8" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9587,10 +9827,10 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="8" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9637,10 +9877,10 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" s="8" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9689,14 +9929,14 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" s="8" t="inlineStr">
+      <c r="N40" s="10" t="inlineStr">
         <is>
           <t>(전일) 유나이티드렌털스(장비 임대): 금리 상승과 건설투자 둔화 우려가 동종업종 압박</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9745,15 +9985,15 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" s="8" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9801,15 +10041,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N42" s="8" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9851,15 +10091,19 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="8" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>스트래티지(비트코인 보유기업): 비트코인이 3개월 최고치인 8만1000달러대로 오르며 보유자산 가치 상승 기대가 커졌다.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9901,15 +10145,15 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" s="8" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9955,15 +10199,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N45" s="8" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10007,10 +10251,14 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" s="8" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr">
+        <is>
+          <t>시에나(광통신 장비사): 분기 매출과 이익은 예상을 웃돌았지만 높은 인공지능 기대와 밸류에이션 부담으로 차익실현이 나왔다.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10063,15 +10311,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N47" s="8" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10115,10 +10363,10 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="8" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10167,14 +10415,14 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" s="8" t="inlineStr">
+      <c r="N49" s="10" t="inlineStr">
         <is>
           <t>(전일) 뉴트리엔(비료·칼륨): 질소비료 수급 긴축과 농산물 가격 강세</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10223,10 +10471,10 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" s="8" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10273,10 +10521,10 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" s="8" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10329,15 +10577,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N52" s="8" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10381,10 +10629,10 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="8" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10437,14 +10685,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N54" s="8" t="inlineStr">
+      <c r="N54" s="10" t="inlineStr">
         <is>
           <t>(전일) 바이오젠(신경질환 치료제): 알츠하이머 치료제 캐나다 급여 기대가 지지</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10497,19 +10745,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N55" s="8" t="inlineStr">
+      <c r="N55" s="10" t="inlineStr">
         <is>
           <t>(전일) 셰니어파트너스(LNG 터미널): CCL 3단계 완공으로 현금흐름 기대가 높아졌다.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10551,15 +10799,19 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="8" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr">
+        <is>
+          <t>엘빗시스템즈(방산 전자업체): 특별한 당일 뉴스 없이 최근 상승 이후 차익실현이 이어졌다.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10607,15 +10859,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N57" s="8" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10659,10 +10911,10 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" s="8" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10715,15 +10967,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N59" s="8" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10767,15 +11019,15 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="8" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10823,10 +11075,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="8" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10873,19 +11125,19 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" s="8" t="inlineStr">
+      <c r="N62" s="10" t="inlineStr">
         <is>
           <t>(전일) 선벨트렌털스(산업장비 임대): 개별 악재 없이 금리 상승과 경기민감주 약세 추정</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10929,10 +11181,14 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="8" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr">
+        <is>
+          <t>서클(스테이블코인 발행사): 비트코인이 3개월 최고치로 오르며 가상자산 거래와 스테이블코인 수요 기대가 동반 확대됐다.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10981,15 +11237,15 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="8" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11037,10 +11293,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N65" s="8" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11089,15 +11345,15 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" s="8" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11141,15 +11397,15 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" s="8" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11193,10 +11449,10 @@
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" s="8" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11245,14 +11501,14 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" s="8" t="inlineStr">
+      <c r="N69" s="10" t="inlineStr">
         <is>
           <t>(전일) 엑스피오(LTL 화물운송): 유가 상승과 운송업 경기 우려로 동반 약세</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11301,15 +11557,15 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" s="8" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11353,15 +11609,15 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" s="8" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11405,10 +11661,10 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="8" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11457,14 +11713,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N73" s="8" t="inlineStr">
+      <c r="N73" s="10" t="inlineStr">
         <is>
           <t>(전일) 페덱스프레이트(화물운송): 신규 촉매 없이 운송주 전반의 경기민감 매도</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11517,15 +11773,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N74" s="8" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11573,10 +11829,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N75" s="8" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11625,15 +11881,15 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="8" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11677,10 +11933,14 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" s="8" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr">
+        <is>
+          <t>타이슨푸드(육류 가공사): 미국 소 부족에 따른 소고기 마진 압박으로 연간 매출과 조정 영업이익 전망을 낮췄다.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11733,10 +11993,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N78" s="8" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11789,19 +12049,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N79" s="8" t="inlineStr">
+      <c r="N79" s="10" t="inlineStr">
         <is>
           <t>(전일) CNH(농기계 제조사): 에버코어의 아웃퍼폼 상향으로 9.2% 급등</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B80" s="7" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11845,10 +12105,14 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="8" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr">
+        <is>
+          <t>엠케이에스(반도체 공정장비): 특별한 당일 뉴스 없이 전자기술 신저가 확산에 동반 하락했다.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11901,15 +12165,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N81" s="8" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11953,10 +12217,10 @@
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" s="8" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12009,19 +12273,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N83" s="8" t="inlineStr">
+      <c r="N83" s="10" t="inlineStr">
         <is>
           <t>(전일) 아머스포츠(스포츠용품): 신규 촉매 없이 소비재 약세와 하락 추세가 지속</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12065,10 +12329,10 @@
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" s="8" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12115,15 +12379,15 @@
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" s="8" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12167,10 +12431,10 @@
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" s="8" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12223,15 +12487,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N87" s="8" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12279,10 +12543,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N88" s="8" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12331,10 +12595,10 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" s="8" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12387,10 +12651,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N90" s="8" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12443,19 +12707,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N91" s="8" t="inlineStr">
+      <c r="N91" s="10" t="inlineStr">
         <is>
           <t>(전일) 레비티(생명과학 장비): 별도 당일 뉴스 없이 헬스케어 강세에 동반 상승</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12495,10 +12759,10 @@
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" s="8" t="inlineStr"/>
+      <c r="N92" s="10" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12547,15 +12811,15 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" s="8" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12603,10 +12867,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N94" s="8" t="inlineStr"/>
+      <c r="N94" s="10" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12655,19 +12919,19 @@
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" s="8" t="inlineStr">
+      <c r="N95" s="10" t="inlineStr">
         <is>
           <t>(전일) 텍스트론(항공우주·방산): 특별한 뉴스 없음. 항공우주주 수급 약화로 추정한다.</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12707,15 +12971,19 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" s="8" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr">
+        <is>
+          <t>서밋테라퓨틱스(항암제 개발사): 이보네시맙이 중국 3상에서 키트루다 대비 전체생존기간을 통계적으로 유의하게 개선했다.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12759,10 +13027,10 @@
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" s="8" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="A98" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12811,15 +13079,15 @@
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" s="8" t="inlineStr"/>
+      <c r="N98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12865,10 +13133,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N99" s="8" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12921,15 +13189,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N100" s="8" t="inlineStr"/>
+      <c r="N100" s="10" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B101" s="7" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12973,10 +13241,10 @@
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" s="8" t="inlineStr"/>
+      <c r="N101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13025,15 +13293,15 @@
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
-      <c r="N102" s="8" t="inlineStr"/>
+      <c r="N102" s="10" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13081,10 +13349,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N103" s="8" t="inlineStr"/>
+      <c r="N103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13133,10 +13401,10 @@
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" s="8" t="inlineStr"/>
+      <c r="N104" s="10" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="inlineStr">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13185,10 +13453,10 @@
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" s="8" t="inlineStr"/>
+      <c r="N105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
+      <c r="A106" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13237,10 +13505,10 @@
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" s="8" t="inlineStr"/>
+      <c r="N106" s="10" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
+      <c r="A107" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13289,15 +13557,15 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" s="8" t="inlineStr"/>
+      <c r="N107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B108" s="7" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13341,15 +13609,15 @@
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
-      <c r="N108" s="8" t="inlineStr"/>
+      <c r="N108" s="10" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13397,15 +13665,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N109" s="8" t="inlineStr"/>
+      <c r="N109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13447,10 +13715,10 @@
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" s="8" t="inlineStr"/>
+      <c r="N110" s="10" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13499,19 +13767,19 @@
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" s="8" t="inlineStr">
+      <c r="N111" s="10" t="inlineStr">
         <is>
           <t>(전일) XP(브라질 온라인 증권사): 브라질 증시 3.05% 급등과 헤알 강세에 동반 상승</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13553,10 +13821,10 @@
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" s="8" t="inlineStr"/>
+      <c r="N112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13605,10 +13873,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N113" s="8" t="inlineStr"/>
+      <c r="N113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13661,7 +13929,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N114" s="8" t="inlineStr"/>
+      <c r="N114" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N114"/>
@@ -13767,7 +14035,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13814,19 +14082,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 패스트리테일링(의류 유통): 일본 증시 전면 약세와 소비주 매도에 하락</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13874,15 +14142,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13926,15 +14194,15 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13978,10 +14246,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>미쓰비시상사(종합상사): 버크셔해서웨이 새 최고경영자가 일본 5대 상사 지분 확대 가능성을 언급했다.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14032,19 +14304,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) NTT(통신): 특별한 회사 뉴스 없음(방어적 통신주 수급 추정)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14088,15 +14360,19 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>미쓰이물산(종합상사): 버크셔해서웨이의 일본 상사주 지분 확대 가능성과 자원가격 강세가 매수세를 자극했다.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14138,15 +14414,15 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14190,15 +14466,19 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>스미토모상사(종합상사): 버크셔해서웨이의 일본 5대 상사 장기보유와 추가매수 가능성 발언에 동반 상승했다.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14246,10 +14526,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14302,19 +14582,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 일본우정(우편·금융): 금융주와 고배당 방어주 선호가 이어짐</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14362,10 +14642,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14414,19 +14694,19 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>(전일) 화낙(산업용 로봇): 금리 상승과 위험회피로 기계주 매도가 확대</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14474,15 +14754,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14530,10 +14810,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14580,19 +14860,19 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr">
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>(전일) 에네오스(정유): 중동 긴장으로 원유가 올라 재고평가와 정유마진 기대가 커졌다.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14636,15 +14916,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14690,15 +14970,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>간사이전력(전력회사): 전력·가스 업종이 3.4% 오르는 가운데 방어적 수요와 최근 상승 추세가 이어졌다.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14742,10 +15026,14 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>스미토모부동산(부동산 개발사): 일본은행의 추가 금리인상 관측과 엔화 강세 속 부동산주 부담이 커졌다.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14794,14 +15082,14 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="8" t="inlineStr">
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>(전일) 레이저텍(반도체 검사장비): 시장 기대를 밑돈 FY27 가이던스 부담 지속</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14854,14 +15142,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>(전일) 팬퍼시픽(돈키호테 운영): 이익전망이 기대에 못 미친 뒤 실망 매도가 이어졌다.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14910,14 +15198,14 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr">
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>(전일) 다이후쿠(물류자동화): 일본 산업기계주 전반의 위험회피 매도에 하락</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14964,19 +15252,19 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="8" t="inlineStr">
+      <c r="N23" s="10" t="inlineStr">
         <is>
           <t>(전일) 이데미쓰(정유·석유화학): 원유 급등으로 재고평가와 정유마진 개선 기대가 반영됐다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15018,10 +15306,14 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>니토리(가구·생활용품 유통): 8월 기존점 매출이 4.4% 증가해 소비 둔화 속 수요 회복 기대가 커졌다.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15074,14 +15366,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr">
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>(전일) 미쓰비시케미컬(종합화학): 외국계 증권사가 중립에서 비중확대로 상향</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15128,7 +15420,7 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="8" t="inlineStr">
+      <c r="N26" s="10" t="inlineStr">
         <is>
           <t>(전일) 니테라(점화플러그·전자부품): 금리·유가 충격의 일본 전면 약세에 하락</t>
         </is>
@@ -15238,7 +15530,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15291,14 +15583,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국공상은행(대형 국유은행): 본토 은행주 강세와 고배당 선호로 최고가</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15351,14 +15643,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국농업은행(대형 국유은행): 본토 은행주 상승세가 이어지며 사상 최고가</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15411,14 +15703,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국건설은행(국유은행): 반기 순익 증가와 중간배당 확대가 배당 매력을 높였다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15471,14 +15763,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국은행(국유은행): 반기 실적과 배당 확대 뒤 재평가 기대가 신고가를 이끌었다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15527,14 +15819,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) 초상은행(소매금융 중심 은행): 본토 은행주 동반 강세로 최고가권 진입</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15587,14 +15879,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 교통은행(대형 국유은행): 금융주 자금 유입 속 52주 최고가 경신</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15647,14 +15939,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) BOC홍콩(은행): 별도 뉴스 없이 홍콩 금융주 신고가 흐름에 동반 상승</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15703,10 +15995,10 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15755,14 +16047,14 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국우정저축은행(국유은행): 반기 실적 뒤 배당 확대 기대가 재평가 매수를 이끌었다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15811,14 +16103,14 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 피아이씨씨손해보험(손해보험): 뱅크오브아메리카의 목표가 상향이 촉매였다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15867,19 +16159,19 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국인민보험그룹(종합보험): 고배당 전략과 계열 손보사 목표가 상향이 부각됐다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15921,15 +16213,19 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>중광핵전력(원자력 발전사): 2분기 순이익 증가와 건설 중 원전의 중장기 성장 기대가 방어적 매수를 불렀다.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15975,10 +16271,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>스와이어퍼시픽(복합기업): 장중 사상 최고가를 기록한 뒤 홍콩 증시 약세와 차익실현으로 하락 전환했다.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -16027,15 +16327,15 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16075,10 +16375,14 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>더블유에이치그룹(육류 가공사): 특별한 당일 뉴스 없이 북미 원재료비와 육류 마진 우려가 이어졌다.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -16129,14 +16433,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>(전일) 사이리스(전기차): 8월 판매량 40% 감소 소식으로 신저가</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -16187,15 +16491,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16239,15 +16543,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>샤오펑(전기차 제조사): 상반기 순손실 확대와 중국 전기차 가격경쟁 우려가 주가에 부담을 줬다.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16291,7 +16599,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>앤커이노베이션(소비자 전자기기): 2분기 순이익이 처음으로 10억위안을 넘고 시장 예상을 웃돌아 매수세가 이어졌다.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N20"/>
@@ -16397,7 +16709,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16450,10 +16762,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16504,14 +16816,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국은행(국유은행): 반기 순익 성장과 고배당 자금 유입으로 사상 최고가를 경신했다.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16558,14 +16870,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 차이나모바일(통신사): 약세장에서 배당·방어주 선호로 신고가</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16614,10 +16926,10 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16664,14 +16976,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) 핑안보험(보험·금융): 보험사 상반기 이익 회복과 투자수익 개선</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16720,10 +17032,10 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16772,14 +17084,14 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국우정저축은행(국유은행): 반기 순익 성장과 배당 확대 기대가 신고가를 이끌었다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16828,19 +17140,19 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국인민보험그룹(손해보험 중심): 상반기 순익과 투자수익 급증으로 보험주 선도</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16882,10 +17194,14 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>중국태평양보험(보험사): 보험 업종이 2.6% 오르는 가운데 방어주와 배당주 선호가 집중됐다.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16938,14 +17254,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 핑안은행(은행): 금융주 강세가 이어지며 52주 신고가 돌파</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16998,10 +17314,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17052,10 +17368,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17106,19 +17422,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>(전일) 선그로우(태양광·저장장치): 상반기 매출 29%, 순이익 32% 감소가 매도를 불렀다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17160,10 +17476,14 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>산둥골드(금광업체): 귀금속 업종 강세와 높은 금 가격에 따른 자체 생산 금의 이익 개선 기대가 이어졌다.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17216,14 +17536,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr">
-        <is>
-          <t>(전일) 난징은행(은행): 중국 금융주 신고가 확산과 배당 선호가 지지</t>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>난징은행(지방은행): 중국 금융주 신고가 확산과 배당 선호가 이어지며 52주 고점을 돌파했다.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17272,14 +17592,14 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>(전일) 상하이국제항만(항만 운영): 특별한 신규 뉴스 없이 항만·국유주 순환매</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17326,10 +17646,10 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17378,19 +17698,19 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr">
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>(전일) 베이징은행(지역은행): 반기 이익 성장과 순이자마진 안정 기대가 재평가를 이끌었다.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17438,10 +17758,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>옴니비전(이미지센서 업체): 반도체 상장지수펀드가 0.6% 하락하고 기술주 차익실현이 이어져 신저가를 기록했다.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17488,14 +17812,14 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>(전일) 국전전력(발전사): 별도 뉴스 없이 방어적 전력주 선호로 신고가</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17544,19 +17868,19 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr">
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>(전일) 동방전기(발전설비): 전력장비주 약세와 위험회피 매도로 하락</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17602,15 +17926,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>동방성홍(정유·화학업체): 뚜렷한 당일 공시 없이 석유화학 수급 개선 기대와 단기 자금 유입으로 급등했다.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17652,10 +17980,14 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>룽위안전력(풍력 발전사): 풍황과 전력가격 압박으로 발전량과 수익성 회복이 지연될 수 있다는 우려가 이어졌다.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17706,14 +18038,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr">
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>(전일) 사이리스(전기차): 8월 판매량 40% 감소와 자동차주 약세로 하락</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17760,7 +18092,7 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N26"/>
